--- a/artfynd/A 47672-2022 artfynd.xlsx
+++ b/artfynd/A 47672-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47672-2022 artfynd.xlsx
+++ b/artfynd/A 47672-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>96444436</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -731,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583729.2407510087</v>
+        <v>583729</v>
       </c>
       <c r="R2" t="n">
-        <v>6319641.00938523</v>
+        <v>6319641</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -804,15 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97620792</v>
+        <v>97620788</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,7 +829,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -860,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583681.2988457275</v>
+        <v>583747</v>
       </c>
       <c r="R3" t="n">
-        <v>6319691.233070926</v>
+        <v>6319760</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -933,15 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97620788</v>
+        <v>97620792</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -968,7 +953,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -989,10 +974,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583746.4807450571</v>
+        <v>583682</v>
       </c>
       <c r="R4" t="n">
-        <v>6319760.076903275</v>
+        <v>6319691</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1065,12 +1050,7 @@
         <v>104505037</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,10 +1098,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583802.7685401746</v>
+        <v>583802</v>
       </c>
       <c r="R5" t="n">
-        <v>6319836.909494825</v>
+        <v>6319837</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1188,6 +1168,130 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104505110</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tålebo 18:1, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>583740</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6319882</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-11-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-11-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47672-2022 artfynd.xlsx
+++ b/artfynd/A 47672-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96444436</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,6 +930,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97620788</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1044,6 +1059,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97620792</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1168,6 +1188,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104505037</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1292,8 +1317,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104505110</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>